--- a/data/trans_camb/P1805_2016_2023-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1805_2016_2023-Clase-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,46</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 5,33</t>
+          <t>-0,6; 4,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 3,9</t>
+          <t>-1,87; 3,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 3,82</t>
+          <t>-0,32; 3,41</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 387,23</t>
+          <t>-30,14; 323,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 144,06</t>
+          <t>-34,86; 137,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 161,07</t>
+          <t>-11,36; 141,73</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,8</t>
+          <t>3,69</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>2,53</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,93</t>
+          <t>-0,64; 3,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,56</t>
+          <t>1,0; 6,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,45</t>
+          <t>0,78; 4,15</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>167,44%</t>
+          <t>162,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124,91%</t>
+          <t>120,42%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 468,5</t>
+          <t>-28,12; 396,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,76; 555,41</t>
+          <t>11,43; 589,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,42; 342,72</t>
+          <t>24,51; 305,59</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-2,47</t>
+          <t>-2,74</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,02</t>
+          <t>-0,28</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,82</t>
+          <t>-1,62; 2,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 1,89</t>
+          <t>-7,74; 1,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,08</t>
+          <t>-2,36; 1,65</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-17,82%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-37,09%</t>
+          <t>-41,11%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-29,45%</t>
+          <t>-8,17%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,21; 94,97</t>
+          <t>-52,05; 194,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,87; 58,48</t>
+          <t>-74,05; 72,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,13; 41,18</t>
+          <t>-51,25; 64,2</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>1,23</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,26</t>
+          <t>0,61; 3,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,2</t>
+          <t>-1,72; 2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,96</t>
+          <t>-0,06; 2,28</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>149,4%</t>
+          <t>156,1%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-18,3%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,08; 366,68</t>
+          <t>29,38; 456,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,22; 32,02</t>
+          <t>-31,24; 70,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 98,62</t>
+          <t>-2,37; 119,32</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-0,12</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,42</t>
+          <t>-1,3; 1,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,09</t>
+          <t>-2,58; 1,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,09</t>
+          <t>-1,31; 1,04</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-18,95%</t>
+          <t>-15,18%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-2,19%</t>
+          <t>-4,4%</t>
         </is>
       </c>
     </row>
@@ -1001,24 +1001,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-49,04; 239,59</t>
+          <t>-58,91; 182,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,9; 42,27</t>
+          <t>-49,01; 38,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 51,51</t>
+          <t>-38,18; 45,24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 9,52</t>
+          <t>-0,42; 10,06</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,09</t>
+          <t>-1,7; 1,8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,82</t>
+          <t>-0,94; 2,6</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>128,84%</t>
+          <t>152,87%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>-1,81%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 887,88</t>
+          <t>-27,95; 722,44</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-44,69; 95,05</t>
+          <t>-44,4; 79,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 130,1</t>
+          <t>-27,39; 103,35</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,94</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,24</t>
+          <t>0,6; 2,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,06</t>
+          <t>-0,4; 1,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,36</t>
+          <t>0,36; 1,55</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>17,14; 150,03</t>
+          <t>27,79; 148,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 31,76</t>
+          <t>-9,82; 40,83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1,92; 54,8</t>
+          <t>11,26; 61,14</t>
         </is>
       </c>
     </row>
